--- a/university_data.xlsx
+++ b/university_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E141"/>
+  <dimension ref="A1:F141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>contacts</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>address</t>
         </is>
       </c>
     </row>
@@ -526,6 +531,14 @@
 info@kainar-edu.kz</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Алматы
+, ул. Байзакова, 125/185 НП 4, угол ул. Айтеке би
+Алматы
+, ул. Байзакова, 125/185 НП 4, угол ул. Айтеке би</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -561,6 +574,14 @@
 +7 700 304 03 36 ,
 +7 707 304 03 36
 mba.alemuniversity@gmail.com</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Астана
+, ​ул.Амман, 8​, 5-й этаж
+Астана
+, ​ул.Амман, 8​, 5-й этаж</t>
         </is>
       </c>
     </row>
@@ -649,6 +670,14 @@
 8 (7222) 44-24-56 ,
 +7 700 64343 56
 semey@abu.edu.kz</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Семей
+, ул. Мәңгілік Ул, 11
+Семей
+, ул. Мәңгілік Ул, 11</t>
         </is>
       </c>
     </row>
@@ -733,6 +762,14 @@
 info@almau.edu.kz
 8 (727) 313 30 40
 info@almau.edu.kz</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Алматы
+, ул. Розыбакиева, 227
+Алматы
+, ул. Розыбакиева, 227</t>
         </is>
       </c>
     </row>
@@ -842,6 +879,14 @@
 info@alt.edu.kz</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Алматы
+, ул. Шевченко, 97
+Алматы
+, ул. Шевченко, 97</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -915,6 +960,14 @@
 +7 (7172) 64‒57‒17</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Астана
+, пр. Мәңгілік Ел, С1
+Астана
+, пр. Мәңгілік Ел, С1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -963,6 +1016,14 @@
 info@qcef.kz
 +7 777 767 0907
 info@qcef.kz</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Астана
+, ул. Сыганак 38/1
+Астана
+, ул. Сыганак 38/1</t>
         </is>
       </c>
     </row>
@@ -1033,6 +1094,14 @@
 cu@cu.edu.kz</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Алматы
+, пр. Достык, 85 А; пр. Сейфуллина, 521
+Алматы
+, пр. Достык, 85 А; пр. Сейфуллина, 521</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1098,6 +1167,14 @@
 +7 700 318 00 23 ,
 +7 700 317 33 33
 info@coventry.edu.kz</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Астана
+, шоссе Коргалжын, 13а
+Астана
+, шоссе Коргалжын, 13а</t>
         </is>
       </c>
     </row>
@@ -1168,6 +1245,14 @@
 +7‒771‒500‒55‒77</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Алматы
+, ​Проспект Аль-Фараби, 120/48
+Алматы
+, ​Проспект Аль-Фараби, 120/48</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1231,6 +1316,14 @@
 info@esil.edu.kz</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Астана
+, ул. А. Жубанова, 7
+Астана
+, ул. А. Жубанова, 7</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1287,6 +1380,14 @@
 8 (7172) 70 30 30 ,
 +7 700 170 30 30
 info@mnu.kz</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Астана
+, шоссе Коргалжын, 8
+Астана
+, шоссе Коргалжын, 8</t>
         </is>
       </c>
     </row>
@@ -1378,6 +1479,14 @@
 undgrad@satbayev.university</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Алматы
+, ул. Сатпаева, 22а
+Алматы
+, ул. Сатпаева, 22а</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1432,6 +1541,14 @@
 8 (727) 307 95 65 ,
 + 7 702 000 11 33 WhatsApp
 info@sdu.edu.kz</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Алматы
+, г. Каскелен, пр. Абылай хана, 1/1
+Алматы
+, г. Каскелен, пр. Абылай хана, 1/1</t>
         </is>
       </c>
     </row>
@@ -1538,6 +1655,14 @@
 +7 777 196 24 42 ,
 +7 708 207 45 05
 talapker@shakarim.kz</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Семей
+, ул. Глинки, 20а
+Семей
+, ул. Глинки, 20а</t>
         </is>
       </c>
     </row>
@@ -1671,6 +1796,14 @@
 pgu@udu.tou.kz</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Павлодар
+, ул. Ломова, 64
+Павлодар
+, ул. Ломова, 64</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1766,6 +1899,14 @@
 ualikhanovadmission@shokan.edu.kz</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Кокшетау
+, ул. Абая, 76
+Кокшетау
+, ул. Абая, 76</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1811,6 +1952,14 @@
 8 (727) 274 49 19 ,
 +7 776 046 68 51
 admission.wsuk@wsu.ac.kr</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Туркестан
+, 160-й квартал, строение 39
+Туркестан
+, 160-й квартал, строение 39</t>
         </is>
       </c>
     </row>
@@ -1913,6 +2062,14 @@
 info@yu.edu.kz</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Актау
+, ​32-й микрорайон
+Актау
+, ​32-й микрорайон</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1989,6 +2146,14 @@
 opr_bolashak@mail.ru</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Караганда
+, ул. Ерубаева, 16
+Караганда
+, ул. Ерубаева, 16</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2044,6 +2209,14 @@
 admission@apa.kz</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Астана
+, пр. Абая, 33а
+Астана
+, пр. Абая, 33а</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2097,6 +2270,14 @@
 office@agakaz.kz</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Алматы
+, ул. Ахметова, 44
+Алматы
+, ул. Ахметова, 44</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2136,6 +2317,14 @@
 kti@emer.kz
 +7 (7162) 25‒13‒36
 kti@emer.kz</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Кокшетау
+, ул. ​Акана-Серi, 136
+Кокшетау
+, ул. ​Акана-Серi, 136</t>
         </is>
       </c>
     </row>
@@ -2206,6 +2395,14 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Алматы
+, ул. Мади, 1Б
+Алматы
+, ул. Мади, 1Б</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2253,6 +2450,14 @@
 info@ang.edu.kz
 +7 (7152) 47‒74‒83
 info@ang.edu.kz</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Петропавловск
+, ул. Кизатова, 6/1
+Петропавловск
+, ул. Кизатова, 6/1</t>
         </is>
       </c>
     </row>
@@ -2302,6 +2507,14 @@
 +7 (727) 264‒65‒29</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Алматы
+, пр. Достык, 103
+Алматы
+, пр. Достык, 103</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2335,6 +2548,14 @@
 +7 700 957 00 62 ,
 +7 700 957 00 68
 admission@apems.edu.kz</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Астана
+, Бизнес-центр «Экспо», пр. Мангилик Ел, В 2.2
+Астана
+, Бизнес-центр «Экспо», пр. Мангилик Ел, В 2.2</t>
         </is>
       </c>
     </row>
@@ -2439,6 +2660,14 @@
 admissions@zhubanov.edu.kz</t>
         </is>
       </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Актобе
+, пр. А. Молдагуловой, 34
+Актобе
+, пр. А. Молдагуловой, 34</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2541,6 +2770,14 @@
 admissions@zhubanov.edu.kz</t>
         </is>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Актобе
+, пр. А. Молдагуловой, 34
+Актобе
+, пр. А. Молдагуловой, 34</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2580,6 +2817,14 @@
         <is>
           <t>+7 (7132) 97‒29‒21
 +7 (7132) 97‒29‒21</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Актобе
+, ​Курсантское шоссе, 1
+Актобе
+, ​Курсантское шоссе, 1</t>
         </is>
       </c>
     </row>
@@ -2635,6 +2880,14 @@
 info@aacademymvd.kz</t>
         </is>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Алматы
+, ул. Утепова, 29
+Алматы
+, ул. Утепова, 29</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2689,6 +2942,14 @@
 info@aesa.kz</t>
         </is>
       </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Алматы
+, ул. Жандосова, 59
+Алматы
+, ул. Жандосова, 59</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2731,6 +2992,14 @@
 +7 778 788 41 94
 8 (7182) 61 33 40 ,
 +7 778 788 41 94</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Павлодар
+, ул. Камзина, 90
+Павлодар
+, ул. Камзина, 90</t>
         </is>
       </c>
     </row>
@@ -2794,6 +3063,14 @@
 info@atu.edu.kz
 +7 707 221 88 08
 info@atu.edu.kz</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Алматы
+, ул. Толе би, 100
+Алматы
+, ул. Толе би, 100</t>
         </is>
       </c>
     </row>
@@ -2883,6 +3160,14 @@
 pk@aues.kz</t>
         </is>
       </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Алматы
+, ул. А.Байтурсынова, 126/1
+Алматы
+, ул. А.Байтурсынова, 126/1</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2927,6 +3212,14 @@
 +7 707 240 10 04 ,
 +7 707 220 37 97
 AFinfo@mephi.ru</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Алматы
+, пр. аль-Фараби, 71
+Алматы
+, пр. аль-Фараби, 71</t>
         </is>
       </c>
     </row>
@@ -2992,6 +3285,14 @@
 8 (71430) 7 11 57 ,
 4 95 02
 arkgpi@mail.ru</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Аркалык
+, ул. Ауельбекова, 17
+Аркалык
+, ул. Ауельбекова, 17</t>
         </is>
       </c>
     </row>
@@ -3081,6 +3382,14 @@
 kense@asu.edu.kz</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Атырау
+, пр. Студенческий, 1
+Атырау
+, пр. Студенческий, 1</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3137,6 +3446,14 @@
 8 (7122) 36-25-56 ,
 +7 701 344 35 47
 info@aogu.edu.kz</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Атырау
+, ул. Баймуханова, 45а
+Атырау
+, ул. Баймуханова, 45а</t>
         </is>
       </c>
     </row>
@@ -3199,6 +3516,14 @@
 +7 (7132) 97‒40‒81 ,
 +7 (7132) 51 15 96
 info@bu.edu.kz</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Актобе
+, ул. ​Братьев Жубановых, 302А
+Актобе
+, ул. ​Братьев Жубановых, 302А</t>
         </is>
       </c>
     </row>
@@ -3252,6 +3577,14 @@
 +7 (727) 303‒69‒14</t>
         </is>
       </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Алматы
+, ул.  Жандосова, 53
+Алматы
+, ул.  Жандосова, 53</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3303,6 +3636,14 @@
 +7 (7132) 97-22-44
 +7 (7132) 97-22-16 ,
 +7 (7132) 97-22-44</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Актобе
+, пр. А.​Молдагуловой, 39
+Актобе
+, пр. А.​Молдагуловой, 39</t>
         </is>
       </c>
     </row>
@@ -3358,6 +3699,14 @@
 info@visv.kz
 +7 (727) 290-16-41
 info@visv.kz</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Алматы
+, ул. Красногорская, 4
+Алматы
+, ул. Красногорская, 4</t>
         </is>
       </c>
     </row>
@@ -3457,6 +3806,14 @@
 8 (7232) 51 08 85 ,
 +7 707 285 50 12
 opr.vkgtu@mail.ru</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Усть-Каменогорск
+, ул. ​Серикбаева, 19
+Усть-Каменогорск
+, ул. ​Серикбаева, 19</t>
         </is>
       </c>
     </row>
@@ -3562,6 +3919,14 @@
 rostvkgu@mail.ru</t>
         </is>
       </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Усть-Каменогорск
+, ул. 30-й Гвардейской дивизии, 34
+Усть-Каменогорск
+, ул. 30-й Гвардейской дивизии, 34</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3609,6 +3974,14 @@
 gumtechak@mail.ru</t>
         </is>
       </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Кокшетау
+, ул. Жамбыла, 35
+Кокшетау
+, ул. Жамбыла, 35</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3655,6 +4028,14 @@
 8 (7172) 56   22 00 ,
 +7 777 691 90 43
 eagi_pk@egi.edu.kz</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Астана
+, пр. М.Жумабаева, 4
+Астана
+, пр. М.Жумабаева, 4</t>
         </is>
       </c>
     </row>
@@ -3774,6 +4155,14 @@
 profenu@mail.ru</t>
         </is>
       </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Астана
+, ул. Сатпаева, 2
+Астана
+, ул. Сатпаева, 2</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3833,6 +4222,14 @@
 pr@etu.edu.kz</t>
         </is>
       </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Алматы
+, ул. Толе би, 109Б
+Алматы
+, ул. Толе би, 109Б</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3862,6 +4259,14 @@
 info@nmu.kz
 +7 (727) 302‒09‒43
 info@nmu.kz</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Алматы
+, пр. Аль-Фараби, 73
+Алматы
+, пр. Аль-Фараби, 73</t>
         </is>
       </c>
     </row>
@@ -3909,6 +4314,12 @@
 eitiekb@mail.ru
 +7 (7187) 76-12-55
 eitiekb@mail.ru</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Экибастуз, ул. Энергетиков, 54А
+Экибастуз, ул. Энергетиков, 54А</t>
         </is>
       </c>
     </row>
@@ -3967,6 +4378,12 @@
 8 (7102) 41 04 61 ,
 +7 777 218 93 25
 univer_zhez@mail.ru</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Жезказган, пр. Алашахана, 1Б
+Жезказган, пр. Алашахана, 1Б</t>
         </is>
       </c>
     </row>
@@ -4054,6 +4471,14 @@
 vuz@zu.edu.kz</t>
         </is>
       </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Талдыкорган
+, ул. И.Жансугурова, 187а
+Талдыкорган
+, ул. И.Жансугурова, 187а</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4131,6 +4556,14 @@
 zapkazatu@wkau.kz</t>
         </is>
       </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Уральск
+, ул. Жангир хана, 51
+Уральск
+, ул. Жангир хана, 51</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4190,6 +4623,14 @@
 wkitu@mail.ru</t>
         </is>
       </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Уральск
+, пр. ​Нурсултана Назарбаева, 194
+Уральск
+, пр. ​Нурсултана Назарбаева, 194</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4243,6 +4684,14 @@
 +7 (7132) 54-48-15 ,
 8-701-765-75-18
 priem@zkmu.kz</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Актобе
+, ул. Маресьева, 68
+Актобе
+, ул. Маресьева, 68</t>
         </is>
       </c>
     </row>
@@ -4339,6 +4788,14 @@
 zapkazu@wku.edu.kz</t>
         </is>
       </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Уральск
+, пр. ​Нурсултана Назарбаева, 162
+Уральск
+, пр. ​Нурсултана Назарбаева, 162</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4419,6 +4876,14 @@
 priem.com@ineu.kz</t>
         </is>
       </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Павлодар
+, ул. Ломова, 45
+Павлодар
+, ул. Ломова, 45</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4475,6 +4940,12 @@
 8 (3842) 58 39 12 ,
 +7 951 583 03 81
 maria_baranova20@mqil.ru</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Кемерово, пр. Советский, 73
+Кемерово, пр. Советский, 73</t>
         </is>
       </c>
     </row>
@@ -4536,6 +5007,12 @@
 priem@kemsu.ru</t>
         </is>
       </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Кемерово, ул. Красная, 6
+Кемерово, ул. Красная, 6</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4575,6 +5052,14 @@
 +7 700 300 17 89 ,
 8 700 300 17 98
 kazsport@inbox.ru</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Алматы
+, пр. Абая, 85
+Алматы
+, пр. Абая, 85</t>
         </is>
       </c>
     </row>
@@ -4632,6 +5117,14 @@
 kaznai@art-oner.kz</t>
         </is>
       </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Алматы
+, ул. Панфилова, 127
+Алматы
+, ул. Панфилова, 127</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4669,6 +5162,14 @@
 info@balletacademy.kz
 +7 (7172) 79‒85‒70
 info@balletacademy.kz</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Астана
+, пр. ​Ұлы Дала, 9
+Астана
+, пр. ​Ұлы Дала, 9</t>
         </is>
       </c>
     </row>
@@ -4711,6 +5212,14 @@
 info@conservatoire.kz
 +7 (727) 277‒64‒92
 info@conservatoire.kz</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Алматы
+, пр. Абылай хана, 86а
+Алматы
+, пр. Абылай хана, 86а</t>
         </is>
       </c>
     </row>
@@ -4763,6 +5272,14 @@
 +7 702 970 33 22 ,
 +7 701 292 22 77
 kazadi@kazadi.kz</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Алматы
+, пр. Райымбека, 415B
+Алматы
+, пр. Райымбека, 415B</t>
         </is>
       </c>
     </row>
@@ -4869,6 +5386,14 @@
 office@kazatu.edu.kz</t>
         </is>
       </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Астана
+, пр. ​Жеңіс, 62
+Астана
+, пр. ​Жеңіс, 62</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4961,6 +5486,14 @@
 info@kaznaru.edu.kz</t>
         </is>
       </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Алматы
+, пр. Абая, 8
+Алматы
+, пр. Абая, 8</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5045,6 +5578,14 @@
 info@kazmkpu.kz</t>
         </is>
       </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Алматы
+, ул. Гоголя, 114/1
+Алматы
+, ул. Гоголя, 114/1</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5088,6 +5629,14 @@
 abiturient@kaznmu.kz
 8 (727) 338-70-27
 abiturient@kaznmu.kz</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Алматы
+, ул. Толе би, 94
+Алматы
+, ул. Толе би, 94</t>
         </is>
       </c>
     </row>
@@ -5204,6 +5753,14 @@
 rector@kaznpu.kz</t>
         </is>
       </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Алматы
+, пр. Достык, 13
+Алматы
+, пр. Достык, 13</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5276,6 +5833,14 @@
 +7 747 722 03 87 ,
 +7 700 452 95 29
 info@kaznuvhi.edu.kz</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Тараз
+, ул. К. Сатбаева, 28
+Тараз
+, ул. К. Сатбаева, 28</t>
         </is>
       </c>
     </row>
@@ -5418,6 +5983,14 @@
 info@kaznu.edu.kz</t>
         </is>
       </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Алматы
+, пр. Аль-Фараби, 71
+Алматы
+, пр. Аль-Фараби, 71</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5514,6 +6087,14 @@
 Kaznui.priem@gmail.com</t>
         </is>
       </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Астана
+, пр. ​Абая, 47
+Астана
+, пр. ​Абая, 47</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5569,6 +6150,14 @@
 8 (727) 292 23 73 ,
 8 (727) 292 08 05
 kazumo@ablaikhan.kz</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Алматы
+, ул. Муратбаева, 200
+Алматы
+, ул. Муратбаева, 200</t>
         </is>
       </c>
     </row>
@@ -5642,6 +6231,14 @@
 8 (7172) 72 58 15 ,
 +7 771 766 99 99, +7 775 232 22 66
 akutb@mail.ru</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Астана
+, ул.К. Мухамедханова, 37а
+Астана
+, ул.К. Мухамедханова, 37а</t>
         </is>
       </c>
     </row>
@@ -5706,6 +6303,14 @@
 kaziitu@mail.ru
 8 (7112) 54‒58‒84
 kaziitu@mail.ru</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Уральск
+, ул. М.Маметовой, 81
+Уральск
+, ул. М.Маметовой, 81</t>
         </is>
       </c>
     </row>
@@ -5773,6 +6378,14 @@
 otvet@msu.kz</t>
         </is>
       </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Астана
+, ул. Кажымукана, 11
+Астана
+, ул. Кажымукана, 11</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5837,6 +6450,14 @@
 kafu_ukg@mail.ru</t>
         </is>
       </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Усть-Каменогорск
+, ул. М.Горького, 76
+Усть-Каменогорск
+, ул. М.Горького, 76</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5892,6 +6513,14 @@
 info@kbtu.kz</t>
         </is>
       </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Алматы
+, ул. Толе би, 59
+Алматы
+, ул. Толе би, 59</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5928,6 +6557,14 @@
 support@kini.kz
 8 (7292) 788 788 (411)
 support@kini.kz</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Актау
+, 32-й микрорайон, офисы Е101, Е104
+Актау
+, 32-й микрорайон, офисы Е101, Е104</t>
         </is>
       </c>
     </row>
@@ -5976,6 +6613,14 @@
 + 7 (727) 355 05 51 (вн. 229) ,
 +7 700 355 05 51
 admission@dku.kz</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Алматы
+, ул. Пушкина, 111
+Алматы
+, ул. Пушкина, 111</t>
         </is>
       </c>
     </row>
@@ -6026,6 +6671,14 @@
 info@medkrmu.kz</t>
         </is>
       </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Алматы
+, пр. Абылай хана, 51/53
+Алматы
+, пр. Абылай хана, 51/53</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6064,6 +6717,14 @@
 +7 727 293 52 95 ,
 +7 727 317-00-53
 info@atu.kz</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Алматы
+, ул. Толе би, 100
+Алматы
+, ул. Толе би, 100</t>
         </is>
       </c>
     </row>
@@ -6119,6 +6780,14 @@
 academy@kpa.gov.kz</t>
         </is>
       </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Караганда
+, ул. Ермекова, 124
+Караганда
+, ул. Ермекова, 124</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6174,6 +6843,14 @@
 8 (7213) 91 65 61 ,
 8 701 430 64 14
 bulletin@tttu.edu.kz</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Темиртау
+, пр. Республики, 30
+Темиртау
+, пр. Республики, 30</t>
         </is>
       </c>
     </row>
@@ -6235,6 +6912,14 @@
 8 (7212) 50 06 35 ,
 50-39-30 (внутр. 1340)
 talapker@qmu.kz</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Караганда
+, ул. Гоголя, 40
+Караганда
+, ул. Гоголя, 40</t>
         </is>
       </c>
     </row>
@@ -6351,6 +7036,14 @@
 priemka@buketov.edu.kz</t>
         </is>
       </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Караганда
+, ул. Университетская, 28
+Караганда
+, ул. Университетская, 28</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6421,6 +7114,14 @@
 032pk_kstu@mail.ru</t>
         </is>
       </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Караганда
+, пр. Нурсултана Назарбаева, 56
+Караганда
+, пр. Нурсултана Назарбаева, 56</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6485,6 +7186,14 @@
 pk@keu.kz</t>
         </is>
       </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Караганда
+, ул. Академическая, 9
+Караганда
+, ул. Академическая, 9</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6539,6 +7248,14 @@
         <is>
           <t>+7 (7172) 50‒18‒31
 +7 (7172) 50‒18‒31</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Астана
+, ул. Кенесары, 60
+Астана
+, ул. Кенесары, 60</t>
         </is>
       </c>
     </row>
@@ -6608,6 +7325,14 @@
 kuam-kokchetau@mail.ru</t>
         </is>
       </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Кокшетау
+, ул. М.Ауэзова, 189а
+Кокшетау
+, ул. М.Ауэзова, 189а</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6643,6 +7368,14 @@
 +7 (7142) 26‒34‒23 ,
 +7 (7142) 26-57-40
 ODO@kostacademy.gov.kz</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Костанай
+, пр. Абая, 11
+Костанай
+, пр. Абая, 11</t>
         </is>
       </c>
     </row>
@@ -6700,6 +7433,14 @@
 pk@kineu.kz
 +7 (7142) 28‒02‒60
 pk@kineu.kz</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Костанай
+, ул. Чернышевского, 59
+Костанай
+, ул. Чернышевского, 59</t>
         </is>
       </c>
     </row>
@@ -6776,6 +7517,14 @@
 info@ksu.edu.kz</t>
         </is>
       </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Костанай
+, ул. А.Байтурсынова, 47
+Костанай
+, ул. А.Байтурсынова, 47</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6841,6 +7590,14 @@
 pkkstu@mail.ru</t>
         </is>
       </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Костанай
+, пр. Кобыланды батыра, 27
+Костанай
+, пр. Кобыланды батыра, 27</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6878,6 +7635,14 @@
 8 (7142) 57 67 99 ,
 +7 708 980 79 98
 kfchelgu@mail.ru</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Костанай
+, ул. Бородина, 168А
+Костанай
+, ул. Бородина, 168А</t>
         </is>
       </c>
     </row>
@@ -6929,6 +7694,14 @@
 07 702 842 93 02 ,
 +7 707 307 28 55
 ashykuniver@mail.ru</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Кызылорда
+, ул. Г. Муратбаева, 72
+Кызылорда
+, ул. Г. Муратбаева, 72</t>
         </is>
       </c>
     </row>
@@ -7058,6 +7831,14 @@
 ksu@korkyt.kz</t>
         </is>
       </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Кызылорда
+, ул. Айтеке Би, 29А
+Кызылорда
+, ул. Айтеке Би, 29А</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7098,6 +7879,14 @@
 +7 701 837 77 67 ,
 +7 495 234 83 87
 astana@inno.mgimo.ru</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Астана
+, ул. Кажимукана, 11
+Астана
+, ул. Кажимукана, 11</t>
         </is>
       </c>
     </row>
@@ -7147,6 +7936,14 @@
 abiturient@amu.kz</t>
         </is>
       </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Астана
+, ул. ​Бейбітшілік, 49а
+Астана
+, ул. ​Бейбітшілік, 49а</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7190,6 +7987,14 @@
 smu@nao-mus.kz</t>
         </is>
       </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Семей
+, ул. Абая, 103
+Семей
+, ул. Абая, 103</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7217,6 +8022,14 @@
         <is>
           <t>+7 (7182) 55‒28‒54
 +7 (7182) 55‒28‒54</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Павлодар
+, ул. Торайгырова, 72/1
+Павлодар
+, ул. Торайгырова, 72/1</t>
         </is>
       </c>
     </row>
@@ -7306,6 +8119,14 @@
 info@mok.kz</t>
         </is>
       </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Алматы
+, ул. Рыскулбекова, 28
+Алматы
+, ул. Рыскулбекова, 28</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7371,6 +8192,14 @@
 info@metu.kz</t>
         </is>
       </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Алматы
+, пр. Аль-Фараби, 93Г/5
+Алматы
+, пр. Аль-Фараби, 93Г/5</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7434,6 +8263,14 @@
 info@metu.kz
 +7 775 007 50 55
 info@metu.kz</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Алматы
+, пр. Аль-Фараби, 93Г/5
+Алматы
+, пр. Аль-Фараби, 93Г/5</t>
         </is>
       </c>
     </row>
@@ -7537,6 +8374,14 @@
 info@ayu.edu.kz</t>
         </is>
       </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Туркестан
+, пр. Б. Саттарханова, 29
+Туркестан
+, пр. Б. Саттарханова, 29</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7603,6 +8448,14 @@
 htu@edu.kz</t>
         </is>
       </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Тараз
+, ул. Желтоксан, 69Б
+Тараз
+, ул. Желтоксан, 69Б</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7672,6 +8525,14 @@
 8  (727) 376 74 78 (вн.555) ,
 +7 705 100 09 66
 pk@mtgu.edu.kz</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Алматы
+, мкр-н Жетысу-1, 32а
+Алматы
+, мкр-н Жетысу-1, 32а</t>
         </is>
       </c>
     </row>
@@ -7757,6 +8618,14 @@
 info@aiu.edu.kz</t>
         </is>
       </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Астана
+, пр. Кабанбай батыра, 8
+Астана
+, пр. Кабанбай батыра, 8</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -7827,6 +8696,14 @@
 reception@iitu.edu.kz</t>
         </is>
       </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Алматы
+, ул. Манаса, 34/1
+Алматы
+, ул. Манаса, 34/1</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -7886,6 +8763,14 @@
 kense@iuth.edu.kz</t>
         </is>
       </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Туркестан
+, ул. Рабиги Султан Бегим, 14А
+Туркестан
+, ул. Рабиги Султан Бегим, 14А</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7930,6 +8815,14 @@
 nu@nu.edu.kz</t>
         </is>
       </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Астана
+, пр. Кабанбай батыра, 53
+Астана
+, пр. Кабанбай батыра, 53</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7961,6 +8854,14 @@
         <is>
           <t>+7 (7172) 26‒36‒79
 +7 (7172) 26‒36‒79</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Астана
+, пр. ​Тұран, 72
+Астана
+, пр. ​Тұран, 72</t>
         </is>
       </c>
     </row>
@@ -8044,6 +8945,14 @@
 kense@ppu.edu.kz</t>
         </is>
       </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Павлодар
+, ул. Олжабай батыра, 60
+Павлодар
+, ул. Олжабай батыра, 60</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -8087,6 +8996,12 @@
 admission@pimunn.net</t>
         </is>
       </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Нижний Новгород, пл. Минина и Пожарского, 10/1
+Нижний Новгород, пл. Минина и Пожарского, 10/1</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -8128,6 +9043,14 @@
 +7 777 0 533  533 ,
 +7 707 305 76 27
 priemkz@muctr.ru</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Тараз
+, пр. Толе Би, 62
+Тараз
+, пр. Толе Би, 62</t>
         </is>
       </c>
     </row>
@@ -8180,6 +9103,14 @@
 abiturient@rii.kz</t>
         </is>
       </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Рудный
+, ул. 50 лет Октября, 38
+Рудный
+, ул. 50 лет Октября, 38</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8223,6 +9154,14 @@
 info@gup.kz
 8 (727) 345-35-03
 info@gup.kz</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Алматы
+, ул. Чайковского, 9/11
+Алматы
+, ул. Чайковского, 9/11</t>
         </is>
       </c>
     </row>
@@ -8326,6 +9265,14 @@
 +7 747 806 09 01 ,
 +7 707 182 58 99
 admission@ku.edu.kz</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Петропавловск
+, ул. Пушкина, 86
+Петропавловск
+, ул. Пушкина, 86</t>
         </is>
       </c>
     </row>
@@ -8435,6 +9382,14 @@
 talapker@dulaty.kz</t>
         </is>
       </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Тараз
+, пр. Төле би, 60
+Тараз
+, пр. Төле би, 60</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -8525,6 +9480,14 @@
 8 (727) 377 11 11 ,
 +7 747 364 88 99
 admission@narxoz.kz</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Алматы
+, ул. Жандосова, 55
+Алматы
+, ул. Жандосова, 55</t>
         </is>
       </c>
     </row>
@@ -8603,6 +9566,14 @@
 bolashak_5@bolashak-edu.kz</t>
         </is>
       </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Кызылорда
+, пр. Абая, 31
+Кызылорда
+, пр. Абая, 31</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -8668,6 +9639,14 @@
 info@miras.edu.kz</t>
         </is>
       </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Шымкент
+, ул. Г.Иляева, 3
+Шымкент
+, ул. Г.Иляева, 3</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -8707,6 +9686,14 @@
 donets.synergy@gmail.com</t>
         </is>
       </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Алматы
+, ​ЖК Жагалау​, ул.Варламова, 33, офис 229
+Алматы
+, ​ЖК Жагалау​, ул.Варламова, 33, офис 229</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -8734,6 +9721,14 @@
 ckt-astana@mail.ru
 +7 778 437 54 85
 ckt-astana@mail.ru</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Астана
+, пр. Жеңіс, 79а (Бизнес-центр «АКА»), офис 203
+Астана
+, пр. Жеңіс, 79а (Бизнес-центр «АКА»), офис 203</t>
         </is>
       </c>
     </row>
@@ -8803,6 +9798,14 @@
 info@turan-edu.kz
 +7 (727) 260‒40‒00
 info@turan-edu.kz</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Алматы
+, ул. ​Сатпаева, 16а
+Алматы
+, ул. ​Сатпаева, 16а</t>
         </is>
       </c>
     </row>
@@ -8881,6 +9884,14 @@
 8 (7252) 95‒25‒83 ,
 8 (7252) 95‒25‒84
 info@kipudn.kz</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Шымкент
+, ул. Толе би, 32
+Шымкент
+, ул. Толе би, 32</t>
         </is>
       </c>
     </row>
@@ -8960,6 +9971,14 @@
 info@tashenev.edu.kz</t>
         </is>
       </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Шымкент
+, пр. Д.Конаева, 21
+Шымкент
+, пр. Д.Конаева, 21</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -9016,6 +10035,14 @@
 8 (727) 270 42 48 ,
 +7 707 170 42 13
 uao@kimep.kz</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Алматы
+, пр. Абая, 2
+Алматы
+, пр. Абая, 2</t>
         </is>
       </c>
     </row>
@@ -9082,6 +10109,14 @@
 +7-701-513 11 55 ,
 +7-701-233 58 88
 vuzkunaeva@vuzkunaeva.kz</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Алматы
+, ул. Курмангазы, 107, угол ул. Байтурсынова
+Алматы
+, ул. Курмангазы, 107, угол ул. Байтурсынова</t>
         </is>
       </c>
     </row>
@@ -9153,6 +10188,14 @@
 uib@uib.kz</t>
         </is>
       </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Алматы
+, пр. Абая, 8а
+Алматы
+, пр. Абая, 8а</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -9224,6 +10267,14 @@
 +7 702 912 39 97 ,
 +7 700 139 51 10
 admissions@tau-edu.kz</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Астана
+, ул.  Ы. Дукенулы, 29
+Астана
+, ул.  Ы. Дукенулы, 29</t>
         </is>
       </c>
     </row>
@@ -9309,6 +10360,12 @@
 +7 908 900 85 01 Серова Елена Юрьевна ,
 +7 800 350 61-10 (звонок бесплатный)
 pkusfeu@yandex.ru</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Екатеринбург, ул. Сибирский тракт, 37
+Екатеринбург, ул. Сибирский тракт, 37</t>
         </is>
       </c>
     </row>
@@ -9384,6 +10441,12 @@
 priem@urfu.ru</t>
         </is>
       </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Екатеринбург, ул. Мира, 19
+Екатеринбург, ул. Мира, 19</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -9465,6 +10528,14 @@
 info@caiu.edu.kz</t>
         </is>
       </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Шымкент
+, ул. А. Байтурсынова, 80
+Шымкент
+, ул. А. Байтурсынова, 80</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -9505,6 +10576,14 @@
 cka_kz@mail.ru
 +7 (7212) 47‒50‒69
 cka_kz@mail.ru</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Караганда
+, ул. Пичугина, 259
+Караганда
+, ул. Пичугина, 259</t>
         </is>
       </c>
     </row>
@@ -9594,6 +10673,14 @@
 shu2050@mail.ru</t>
         </is>
       </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Шымкент
+, ул. Жибек жолы, 6
+Шымкент
+, ул. Жибек жолы, 6</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -9636,6 +10723,14 @@
 medacadem@rambler.ru
 (7252) 39-57-57
 medacadem@rambler.ru</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Шымкент
+, пл. Аль-Фараби, 1/1
+Шымкент
+, пл. Аль-Фараби, 1/1</t>
         </is>
       </c>
     </row>
@@ -9799,6 +10894,14 @@
 pk_ukgu@mail.ru</t>
         </is>
       </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Шымкент
+, пр. Тауке хана, 5
+Шымкент
+, пр. Тауке хана, 5</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -9896,6 +10999,14 @@
 info@okmpu.kz</t>
         </is>
       </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Шымкент
+, ул. А.Байтурсынова, 13
+Шымкент
+, ул. А.Байтурсынова, 13</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
